--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MARYLAND_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MARYLAND_2013.xlsx
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C108">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C398">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C459">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C480">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C789">
